--- a/marketing_surveys/018_digital_marketing_survey--marketing_surveys.xlsx
+++ b/marketing_surveys/018_digital_marketing_survey--marketing_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'everyday'}</t>
+          <t>everyday</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Everyday'}</t>
+          <t>Everyday</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'several_times_a_month'}</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Several times a month'}</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'customer'}</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Customer'}</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'everyday'}</t>
+          <t>everyday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Everyday'}</t>
+          <t>Everyday</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'several_times_a_month'}</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Several times a month'}</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'customer'}</t>
+          <t>customer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Customer'}</t>
+          <t>Customer</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
